--- a/data/hypersomnolence_data_sunburst.xlsx
+++ b/data/hypersomnolence_data_sunburst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vpmartin/Documents/VMBox/logi/content_analyses/hypersomnolence.content.analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD77F48B-66EF-A547-A761-F5F12F3D2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3CB1E-CEA8-F543-B756-9D9B3FD81DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="96">
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Subcategory</t>
-  </si>
-  <si>
     <t>Ab</t>
   </si>
   <si>
@@ -97,9 +91,6 @@
     <t>Distress</t>
   </si>
   <si>
-    <t>Mental symptoms</t>
-  </si>
-  <si>
     <t>Worying</t>
   </si>
   <si>
@@ -308,15 +299,31 @@
   </si>
   <si>
     <t>Hypnopompic&lt;br&gt;hallucinations</t>
+  </si>
+  <si>
+    <t>Mental/cognitive symptoms</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Subdimension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -450,30 +457,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -786,57 +794,57 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -868,16 +876,16 @@
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -909,16 +917,16 @@
     </row>
     <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -950,16 +958,16 @@
     </row>
     <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -991,16 +999,16 @@
     </row>
     <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1032,16 +1040,16 @@
     </row>
     <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1073,13 +1081,13 @@
     </row>
     <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8">
@@ -1112,168 +1120,168 @@
     </row>
     <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1305,16 +1313,16 @@
     </row>
     <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1346,16 +1354,16 @@
     </row>
     <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1387,16 +1395,16 @@
     </row>
     <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1428,16 +1436,16 @@
     </row>
     <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1469,16 +1477,16 @@
     </row>
     <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1510,16 +1518,16 @@
     </row>
     <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1551,16 +1559,16 @@
     </row>
     <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1592,16 +1600,16 @@
     </row>
     <row r="21" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1633,13 +1641,13 @@
     </row>
     <row r="22" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22">
@@ -1672,13 +1680,13 @@
     </row>
     <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23">
@@ -1711,13 +1719,13 @@
     </row>
     <row r="24" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24">
@@ -1750,13 +1758,13 @@
     </row>
     <row r="25" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="C25" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25">
@@ -1789,13 +1797,13 @@
     </row>
     <row r="26" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26">
@@ -1828,16 +1836,16 @@
     </row>
     <row r="27" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1869,16 +1877,16 @@
     </row>
     <row r="28" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1910,16 +1918,16 @@
     </row>
     <row r="29" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1951,16 +1959,16 @@
     </row>
     <row r="30" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1992,16 +2000,16 @@
     </row>
     <row r="31" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2033,16 +2041,16 @@
     </row>
     <row r="32" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2074,16 +2082,16 @@
     </row>
     <row r="33" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2115,16 +2123,16 @@
     </row>
     <row r="34" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2156,16 +2164,16 @@
     </row>
     <row r="35" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2197,5 +2205,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>